--- a/ig/DM-JANVIER-2025/CodeSystem-terminologie-sms.xlsx
+++ b/ig/DM-JANVIER-2025/CodeSystem-terminologie-sms.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-12</t>
+    <t>2025-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-09T15:50:00+00:00</t>
+    <t>2025-01-10T13:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,7 +112,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>68735</t>
+    <t>69231</t>
   </si>
   <si>
     <t>Code</t>
